--- a/tables/Table S5.xlsx
+++ b/tables/Table S5.xlsx
@@ -593,7 +593,7 @@
       <c r="B2" s="17" t="n"/>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>edf</t>
+          <t>edf / df</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>edf</t>
+          <t>edf / df</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">

--- a/tables/Table S5.xlsx
+++ b/tables/Table S5.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5980" yWindow="2880" windowWidth="27240" windowHeight="16180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3000" yWindow="2380" windowWidth="27240" windowHeight="16180" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -43,11 +43,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="12"/>
-    </font>
-    <font>
       <name val="Times New Roman"/>
       <family val="1"/>
       <color rgb="FF000000"/>
@@ -56,7 +51,15 @@
     <font>
       <name val="Times New Roman"/>
       <family val="1"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <vertAlign val="subscript"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <i val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -109,53 +112,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,70 +552,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col width="13.6640625" customWidth="1" style="4" min="1" max="1"/>
-    <col width="44.33203125" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="5" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="6.83203125" customWidth="1" style="4" min="4" max="4"/>
-    <col width="6" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
-    <col width="5" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
-    <col width="6.83203125" bestFit="1" customWidth="1" style="4" min="7" max="7"/>
-    <col width="6" bestFit="1" customWidth="1" style="4" min="8" max="8"/>
+    <col width="13.6640625" customWidth="1" style="8" min="1" max="1"/>
+    <col width="13.33203125" bestFit="1" customWidth="1" style="8" min="2" max="2"/>
+    <col width="5" bestFit="1" customWidth="1" style="8" min="3" max="3"/>
+    <col width="6.83203125" customWidth="1" style="8" min="4" max="4"/>
+    <col width="6" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="5" bestFit="1" customWidth="1" style="8" min="6" max="6"/>
+    <col width="6.83203125" bestFit="1" customWidth="1" style="8" min="7" max="7"/>
+    <col width="6" bestFit="1" customWidth="1" style="8" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GAMM Result</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Response (Test)</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Orbicella faveolata</t>
         </is>
       </c>
-      <c r="E1" s="17" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="9" t="n"/>
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>Siderastrea siderea</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" s="4">
-      <c r="B2" s="17" t="n"/>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>edf / df</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
+    <row r="2" ht="28" customHeight="1" s="8">
+      <c r="B2" s="9" t="n"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>edf</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Test Statistic</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>edf / df</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>edf</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Test Statistic</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>p</t>
         </is>
@@ -625,119 +624,176 @@
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Smooth Significance (Photosynthesis All Treatments)</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Time (overall trajectory)</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="n">
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>V</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>M</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>, Pre-Heat (Smooth Terms)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
         <v>4.208</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="14" t="n">
         <v>8.124000000000001</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n">
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>4.72</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="14" t="n">
         <v>31.042</v>
       </c>
-      <c r="H3" s="12" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Treatment × Time</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="6" t="n">
         <v>13.51</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="14" t="n">
         <v>5.894</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="n">
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>13.547</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="14" t="n">
         <v>7.198</v>
       </c>
-      <c r="H4" s="12" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Site × Time</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="6" t="n">
         <v>9.359999999999999</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="14" t="n">
         <v>7.432</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>9.313000000000001</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="14" t="n">
         <v>0.855</v>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Fragment (random smooth)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Fragment</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>105.718</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="14" t="n">
         <v>15.649</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
         <v>140.869</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="14" t="n">
         <v>7.622</v>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
@@ -746,193 +802,186 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Smooth Significance (Photosynthesis Heat Treatments)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Time (overall trajectory)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>V</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>/</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <i val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>F</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+              <vertAlign val="subscript"/>
+            </rPr>
+            <t>M</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Times New Roman"/>
+              <family val="1"/>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t>, Heat Stress (Smooth Terms)</t>
+          </r>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>4.216</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="14" t="n">
         <v>13.659</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
         <v>9.531000000000001</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="14" t="n">
         <v>7.672</v>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Treatment × Time</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="6" t="n">
         <v>8.028</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="14" t="n">
         <v>2.306</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="15" t="n">
         <v>0.011</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="6" t="n">
         <v>5.862</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="14" t="n">
         <v>1.157</v>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Site × Time</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="6" t="n">
         <v>7.332</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="14" t="n">
         <v>3.657</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n">
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n">
         <v>16.079</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="14" t="n">
         <v>3.018</v>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Fragment (random smooth)</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Fragment</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
         <v>105.65</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="14" t="n">
         <v>1.598</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n">
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
         <v>229.937</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="14" t="n">
         <v>2.893</v>
       </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Urban vs Reef Contrast (Time-Averaged Fv/Fm)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>All Treatments</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>175.2</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>9.333</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>295.6</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>1.264</v>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>ns</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Heat Treatments</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>412.8</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>4.188</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>445.6</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>ns</t>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A11:A12"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
